--- a/inst/shiny-examples/MassIBItools/Extras/tables/IDEM_Index_Info_Orig.xlsx
+++ b/inst/shiny-examples/MassIBItools/Extras/tables/IDEM_Index_Info_Orig.xlsx
@@ -8,20 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben.Block\OneDrive - Tetra Tech, Inc\GitHub\IDEMtools\inst\shiny-examples\MassIBItools\Extras\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="600" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{CBC6C1D0-AE70-48D4-B981-77793EEB13B6}"/>
+  <xr:revisionPtr revIDLastSave="639" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{9450A2F1-FDC0-46FC-A0C2-D875F6FBC3AF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="2460" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Bug_N" sheetId="1" r:id="rId1"/>
-    <sheet name="Bug_NC" sheetId="2" r:id="rId2"/>
-    <sheet name="Bug_SW" sheetId="3" r:id="rId3"/>
-    <sheet name="Bug_SE" sheetId="4" r:id="rId4"/>
-    <sheet name="Fish_WS" sheetId="5" r:id="rId5"/>
-    <sheet name="Fish_WL" sheetId="6" r:id="rId6"/>
-    <sheet name="Fish_BL" sheetId="7" r:id="rId7"/>
-    <sheet name="Fish_BH" sheetId="8" r:id="rId8"/>
+    <sheet name="Unique_Bug_Metrics" sheetId="9" r:id="rId1"/>
+    <sheet name="Bug_N" sheetId="1" r:id="rId2"/>
+    <sheet name="Bug_NC" sheetId="2" r:id="rId3"/>
+    <sheet name="Bug_SW" sheetId="3" r:id="rId4"/>
+    <sheet name="Bug_SE" sheetId="4" r:id="rId5"/>
+    <sheet name="Fish_WS" sheetId="5" r:id="rId6"/>
+    <sheet name="Fish_WL" sheetId="6" r:id="rId7"/>
+    <sheet name="Fish_BL" sheetId="7" r:id="rId8"/>
+    <sheet name="Fish_BH" sheetId="8" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Unique_Bug_Metrics!$A$1:$A$21</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="131">
   <si>
     <t>Metric (abbrev)</t>
   </si>
@@ -370,6 +374,69 @@
   </si>
   <si>
     <t>% Insectivore and invertivore individuals (pi_insinv)</t>
+  </si>
+  <si>
+    <t>Bug_Metrics</t>
+  </si>
+  <si>
+    <t>pt_NonIns</t>
+  </si>
+  <si>
+    <t>pi_EPT</t>
+  </si>
+  <si>
+    <t>pi_ffg_pred</t>
+  </si>
+  <si>
+    <t>nt_habit_cling</t>
+  </si>
+  <si>
+    <t>nt_tv_intol</t>
+  </si>
+  <si>
+    <t>pt_tv_toler</t>
+  </si>
+  <si>
+    <t>pi_dom03</t>
+  </si>
+  <si>
+    <t>pi_EPTNoBaeHydro</t>
+  </si>
+  <si>
+    <t>pi_Chiro</t>
+  </si>
+  <si>
+    <t>pi_ffg_shred</t>
+  </si>
+  <si>
+    <t>pi_tv_intol</t>
+  </si>
+  <si>
+    <t>nt_EPT</t>
+  </si>
+  <si>
+    <t>pi_NonIns</t>
+  </si>
+  <si>
+    <t>nt_ffg_scrap</t>
+  </si>
+  <si>
+    <t>pi_ffg_filt</t>
+  </si>
+  <si>
+    <t>pi_habit_cling</t>
+  </si>
+  <si>
+    <t>pt_EPT</t>
+  </si>
+  <si>
+    <t>pi_Odon</t>
+  </si>
+  <si>
+    <t>pi_ffg_colomn</t>
+  </si>
+  <si>
+    <t>pt_tv_intol</t>
   </si>
 </sst>
 </file>
@@ -450,7 +517,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -725,11 +813,137 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A06E358-6A79-4EE7-92C2-A897DB779724}">
+  <dimension ref="A1:A21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:A21" xr:uid="{B53E4E57-49EB-44FC-8C2F-0262479C70B6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A21">
+      <sortCondition ref="A1:A21"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="A1:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="29.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="41.85546875" customWidth="1"/>
+    <col min="1" max="1" width="50" customWidth="1"/>
     <col min="3" max="3" width="41.42578125" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" customWidth="1"/>
     <col min="5" max="5" width="17.42578125" customWidth="1"/>
@@ -860,7 +1074,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1D1177-BF58-4690-B0F3-E4B8B9C44B80}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1030,7 +1244,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71BD45DD-C9A0-4868-ABC6-135358DC1150}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1182,7 +1396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30AE666A-6F6C-4CC2-A2DC-6E828F6056A7}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1335,7 +1549,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{588ADA60-339A-4CB8-94EA-E826EAEBFF0A}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1479,7 +1693,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00690039-BC6A-4645-958A-044B1BAF5C2A}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1600,7 +1814,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AA0657-29F5-4616-9040-346197EC86A3}">
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1732,7 +1946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78449ECD-F460-41A5-AB1D-5EAA5A7C52BF}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/inst/shiny-examples/MassIBItools/Extras/tables/IDEM_Index_Info_Orig.xlsx
+++ b/inst/shiny-examples/MassIBItools/Extras/tables/IDEM_Index_Info_Orig.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben.Block\OneDrive - Tetra Tech, Inc\GitHub\IDEMtools\inst\shiny-examples\MassIBItools\Extras\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="639" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{9450A2F1-FDC0-46FC-A0C2-D875F6FBC3AF}"/>
+  <xr:revisionPtr revIDLastSave="696" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{120A9DC0-A696-404B-9366-4C2CBE5B849B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="2460" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Unique_Bug_Metrics" sheetId="9" r:id="rId1"/>
+    <sheet name="Unique_Metrics" sheetId="9" r:id="rId1"/>
     <sheet name="Bug_N" sheetId="1" r:id="rId2"/>
     <sheet name="Bug_NC" sheetId="2" r:id="rId3"/>
     <sheet name="Bug_SW" sheetId="3" r:id="rId4"/>
@@ -24,7 +24,7 @@
     <sheet name="Fish_BH" sheetId="8" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Unique_Bug_Metrics!$A$1:$A$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Unique_Metrics!$A$1:$A$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,8 +43,80 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={87931BC6-4FCF-4536-ADE8-EB6319DD6D74}</author>
+  </authors>
+  <commentList>
+    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{87931BC6-4FCF-4536-ADE8-EB6319DD6D74}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Should 5th and 95th percentiles be the same? Or is this an error?</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={39A0D1F3-D27A-4D29-A0F3-33DF2CA0AB49}</author>
+  </authors>
+  <commentList>
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{39A0D1F3-D27A-4D29-A0F3-33DF2CA0AB49}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Needs to be added to BioMonTools</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={0D2217BD-EB29-4AD6-A62E-B74212802AFF}</author>
+  </authors>
+  <commentList>
+    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{0D2217BD-EB29-4AD6-A62E-B74212802AFF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Need distance fished (in meters?)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={6547AEC8-01C4-49D8-8447-5E5958A102A4}</author>
+  </authors>
+  <commentList>
+    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{6547AEC8-01C4-49D8-8447-5E5958A102A4}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Wow is this a confusing metric. Needs biomass and distance fished?</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="159">
   <si>
     <t>Metric (abbrev)</t>
   </si>
@@ -437,13 +509,97 @@
   </si>
   <si>
     <t>pt_tv_intol</t>
+  </si>
+  <si>
+    <t>jnt_native</t>
+  </si>
+  <si>
+    <t>jnt_dartmadsculp</t>
+  </si>
+  <si>
+    <t>jni_total</t>
+  </si>
+  <si>
+    <t>pi_CyprinNoCarp</t>
+  </si>
+  <si>
+    <t>pi_osbh_lithophil</t>
+  </si>
+  <si>
+    <t>jpi_headwater</t>
+  </si>
+  <si>
+    <t>pi_pioneer</t>
+  </si>
+  <si>
+    <t>jnt_natinvert</t>
+  </si>
+  <si>
+    <t>jpt_toler</t>
+  </si>
+  <si>
+    <t>pi_delt</t>
+  </si>
+  <si>
+    <t>jnt_darter</t>
+  </si>
+  <si>
+    <t>nt_Cyprin</t>
+  </si>
+  <si>
+    <t>ni_Total_perdist</t>
+  </si>
+  <si>
+    <t>pi_sunfish</t>
+  </si>
+  <si>
+    <t>pi_omnivore</t>
+  </si>
+  <si>
+    <t>jpi_toler</t>
+  </si>
+  <si>
+    <t>pi_rbs</t>
+  </si>
+  <si>
+    <t>pi_dom01</t>
+  </si>
+  <si>
+    <t>BioNatNonTolnGS_perdist</t>
+  </si>
+  <si>
+    <t>nt_natCypinvert</t>
+  </si>
+  <si>
+    <t>pi_intolerant</t>
+  </si>
+  <si>
+    <t>pb_toler</t>
+  </si>
+  <si>
+    <t>pi_os_lithophil</t>
+  </si>
+  <si>
+    <t>nt_darter</t>
+  </si>
+  <si>
+    <t>nt_Cent</t>
+  </si>
+  <si>
+    <t>pb_rbs</t>
+  </si>
+  <si>
+    <t>pi_insinv</t>
+  </si>
+  <si>
+    <t>Fish_Metrics</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -458,6 +614,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -498,7 +660,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -513,6 +675,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,6 +712,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Block, Ben" id="{7C4D4E7C-89FD-4EAE-AABE-B93130019FB5}" userId="S::BEN.BLOCK@tetratech.com::37425d1b-7ac5-49ca-ad9d-3897ecb572d0" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -812,117 +981,248 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C7" dT="2021-01-13T13:33:31.72" personId="{7C4D4E7C-89FD-4EAE-AABE-B93130019FB5}" id="{87931BC6-4FCF-4536-ADE8-EB6319DD6D74}">
+    <text>Should 5th and 95th percentiles be the same? Or is this an error?</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A6" dT="2021-01-13T13:34:01.76" personId="{7C4D4E7C-89FD-4EAE-AABE-B93130019FB5}" id="{39A0D1F3-D27A-4D29-A0F3-33DF2CA0AB49}">
+    <text>Needs to be added to BioMonTools</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A4" dT="2021-01-13T13:55:14.11" personId="{7C4D4E7C-89FD-4EAE-AABE-B93130019FB5}" id="{0D2217BD-EB29-4AD6-A62E-B74212802AFF}">
+    <text>Need distance fished (in meters?)</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A5" dT="2021-01-13T13:55:44.85" personId="{7C4D4E7C-89FD-4EAE-AABE-B93130019FB5}" id="{6547AEC8-01C4-49D8-8447-5E5958A102A4}">
+    <text>Wow is this a confusing metric. Needs biomass and distance fished?</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A06E358-6A79-4EE7-92C2-A897DB779724}">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.140625" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>116</v>
+      </c>
+      <c r="B21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -931,8 +1231,11 @@
       <sortCondition ref="A1:A21"/>
     </sortState>
   </autoFilter>
+  <conditionalFormatting sqref="B2:B28">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -943,10 +1246,11 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="29.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1075,15 +1379,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1D1177-BF58-4690-B0F3-E4B8B9C44B80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1D1177-BF58-4690-B0F3-E4B8B9C44B80}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="68" customWidth="1"/>
+    <col min="1" max="1" width="67.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1241,6 +1545,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1249,10 +1554,11 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="76.28515625" customWidth="1"/>
-    <col min="2" max="3" width="26.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="67.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1397,14 +1703,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30AE666A-6F6C-4CC2-A2DC-6E828F6056A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30AE666A-6F6C-4CC2-A2DC-6E828F6056A7}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="69" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="5" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="67.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1493,19 +1800,19 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>0</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>23.9</v>
       </c>
     </row>
@@ -1546,6 +1853,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1554,10 +1862,11 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="81.85546875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="80.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43.5703125" style="5" customWidth="1"/>
-    <col min="4" max="5" width="29.140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="10" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
@@ -1694,14 +2003,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00690039-BC6A-4645-958A-044B1BAF5C2A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00690039-BC6A-4645-958A-044B1BAF5C2A}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.85546875" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" customWidth="1"/>
-    <col min="4" max="5" width="26.140625" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="74.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1811,18 +2121,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AA0657-29F5-4616-9040-346197EC86A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AA0657-29F5-4616-9040-346197EC86A3}">
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="83.28515625" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="5" width="24.28515625" customWidth="1"/>
+    <col min="1" max="1" width="84.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1854,13 +2166,13 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1887,13 +2199,13 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1943,6 +2255,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1951,10 +2264,11 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.140625" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
-    <col min="3" max="3" width="36.5703125" customWidth="1"/>
-    <col min="4" max="5" width="28.140625" customWidth="1"/>
+    <col min="1" max="1" width="64.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2008,17 +2322,17 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
